--- a/01_Thermal/B_results/four_annular_bemt_tuning_report.xlsx
+++ b/01_Thermal/B_results/four_annular_bemt_tuning_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,488 +436,436 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_rmse</t>
+          <t>raw_wrmse</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_mae</t>
+          <t>raw_sae</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max_rmse</t>
+          <t>n_samples</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>raw_wrmse</t>
+          <t>fan_fourier_order</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>raw_sae</t>
+          <t>fan_robust_loss</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>fan_robust_f_scale</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>FAN_FOURIER_ORDER</t>
+          <t>fan_harmonic_ridge_lambda</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>FAN_ROBUST_LOSS</t>
+          <t>fan_harmonic_rel_cap_lambda</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>FAN_ROBUST_F_SCALE</t>
+          <t>fan_harmonic_rel_max_to_a0</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FAN_HARMONIC_RIDGE_LAMBDA</t>
+          <t>fan_harmonic_order_weight_exp</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>FAN_HARMONIC_REL_CAP_LAMBDA</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>FAN_HARMONIC_REL_MAX_TO_A0</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FAN_HARMONIC_ORDER_WEIGHT_EXP</t>
+          <t>is_selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mixed_soft_l1_cons_split</t>
+          <t>uniform_N2_soft_rmse</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3580463479439127</v>
+        <v>0.333686588563102</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2477869445542598</v>
+        <v>345.1814803740236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4319136672312052</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3359584202335988</v>
-      </c>
-      <c r="F2" t="n">
-        <v>338.2291793165646</v>
-      </c>
-      <c r="G2" t="n">
         <v>1365</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(1.5, 1.5, 1.5, 1.5)</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.05, 0.05, 0.05, 0.05)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.2, 0.2, 0.2, 0.2)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(1.0, 1.5, 1.0, 1.5)</t>
+          <t>(0.7, 0.7, 0.7, 0.7)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>(0.03, 0.03, 0.03, 0.03)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(0.1, 0.1, 0.1, 0.1)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(0.8, 0.8, 0.8, 0.8)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mixed_soft_l1_split</t>
+          <t>uniform_N2_soft_cons</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3583211519416883</v>
+        <v>0.3337472390844793</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2479374213926769</v>
+        <v>344.9414646680535</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4319931022491325</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.3358818723527792</v>
-      </c>
-      <c r="F3" t="n">
-        <v>338.4345802010039</v>
-      </c>
-      <c r="G3" t="n">
         <v>1365</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>(1.5, 1.5, 1.5, 1.5)</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.03, 0.03, 0.03, 0.03)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.1, 0.1, 0.1, 0.1)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>(1.0, 1.5, 1.0, 1.5)</t>
+          <t>(0.8, 0.8, 0.8, 0.8)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>(0.05, 0.03, 0.05, 0.03)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(0.2, 0.1, 0.2, 0.1)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>(0.7, 0.8, 0.7, 0.8)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>uniform_N2_huber_mae</t>
+          <t>mixed_soft_l1_split</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3692686081947913</v>
+        <v>0.3358818723527792</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2446297625344943</v>
+        <v>338.4345802010039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4616923348118198</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3458484047863049</v>
-      </c>
-      <c r="F4" t="n">
-        <v>333.9196258595847</v>
-      </c>
-      <c r="G4" t="n">
         <v>1365</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>(1.0, 1.5, 1.0, 1.5)</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.05, 0.03, 0.05, 0.03)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>('huber', 'huber', 'huber', 'huber')</t>
+          <t>(0.2, 0.1, 0.2, 0.1)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>(0.5, 0.5, 0.5, 0.5)</t>
+          <t>(0.7, 0.8, 0.7, 0.8)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>(0.05, 0.05, 0.05, 0.05)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(0.05, 0.05, 0.05, 0.05)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>(0.7, 0.7, 0.7, 0.7)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uniform_N2_soft_rmse</t>
+          <t>mixed_soft_l1_alt_bias</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3833027008619515</v>
+        <v>0.3358885923134106</v>
       </c>
       <c r="C5" t="n">
-        <v>0.252880205402215</v>
+        <v>343.8421576726826</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5490414114850858</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.333686588563102</v>
-      </c>
-      <c r="F5" t="n">
-        <v>345.1814803740236</v>
-      </c>
-      <c r="G5" t="n">
         <v>1365</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(1.5, 1.0, 1.5, 1.0)</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.03, 0.05, 0.03, 0.05)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.1, 0.2, 0.1, 0.2)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>(0.8, 0.7, 0.8, 0.7)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>(0.05, 0.05, 0.05, 0.05)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(0.2, 0.2, 0.2, 0.2)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>(0.7, 0.7, 0.7, 0.7)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>(1.5, 1.5, 1.5, 1.5)</t>
-        </is>
+      <c r="L5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>uniform_N2_soft_cons</t>
+          <t>mixed_soft_l1_cons_split</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.383313931363289</v>
+        <v>0.3359584202335988</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2527043697201857</v>
+        <v>338.2291793165646</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5490400540866132</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.3337472390844793</v>
-      </c>
-      <c r="F6" t="n">
-        <v>344.9414646680535</v>
-      </c>
-      <c r="G6" t="n">
         <v>1365</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>(1.0, 1.5, 1.0, 1.5)</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.03, 0.03, 0.03, 0.03)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.1, 0.1, 0.1, 0.1)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>(0.8, 0.8, 0.8, 0.8)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>(0.03, 0.03, 0.03, 0.03)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>(0.1, 0.1, 0.1, 0.1)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>(0.8, 0.8, 0.8, 0.8)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>(1.5, 1.5, 1.5, 1.5)</t>
-        </is>
+      <c r="L6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mixed_soft_l1_alt_bias</t>
+          <t>uniform_N2_soft_bal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3865469903595736</v>
+        <v>0.3367884401889317</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2518990166100238</v>
+        <v>342.8112303352777</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5500916809540943</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3358885923134106</v>
-      </c>
-      <c r="F7" t="n">
-        <v>343.8421576726826</v>
-      </c>
-      <c r="G7" t="n">
         <v>1365</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>(1.0, 1.0, 1.0, 1.0)</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.05, 0.05, 0.05, 0.05)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.2, 0.2, 0.2, 0.2)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(1.5, 1.0, 1.5, 1.0)</t>
+          <t>(0.7, 0.7, 0.7, 0.7)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>(0.03, 0.05, 0.03, 0.05)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(0.1, 0.2, 0.1, 0.2)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>(0.8, 0.7, 0.8, 0.7)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>uniform_N2_soft_bal</t>
+          <t>uniform_N2_huber_mae</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3877908024992189</v>
+        <v>0.3458484047863049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2511437584873829</v>
+        <v>333.9196258595847</v>
       </c>
       <c r="D8" t="n">
-        <v>0.550709835297572</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3367884401889317</v>
-      </c>
-      <c r="F8" t="n">
-        <v>342.8112303352777</v>
-      </c>
-      <c r="G8" t="n">
         <v>1365</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(2, 2, 2, 2)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>('huber', 'huber', 'huber', 'huber')</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>(0.5, 0.5, 0.5, 0.5)</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(2, 2, 2, 2)</t>
+          <t>(0.05, 0.05, 0.05, 0.05)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.05, 0.05, 0.05, 0.05)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>(1.0, 1.0, 1.0, 1.0)</t>
+          <t>(0.7, 0.7, 0.7, 0.7)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>(0.05, 0.05, 0.05, 0.05)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>(0.2, 0.2, 0.2, 0.2)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>(0.7, 0.7, 0.7, 0.7)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
           <t>(1.5, 1.5, 1.5, 1.5)</t>
         </is>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -927,57 +875,51 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4124191472146184</v>
+        <v>0.3573173951806795</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2776157915739578</v>
+        <v>378.9455554984523</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5810284901247779</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.3573173951806795</v>
-      </c>
-      <c r="F9" t="n">
-        <v>378.9455554984523</v>
-      </c>
-      <c r="G9" t="n">
         <v>1365</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(1, 1, 1, 1)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>(1.0, 1.0, 1.0, 1.0)</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 1)</t>
+          <t>(0.02, 0.02, 0.02, 0.02)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>('soft_l1', 'soft_l1', 'soft_l1', 'soft_l1')</t>
+          <t>(0.1, 0.1, 0.1, 0.1)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>(0.8, 0.8, 0.8, 0.8)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>(1.0, 1.0, 1.0, 1.0)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>(0.02, 0.02, 0.02, 0.02)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(0.1, 0.1, 0.1, 0.1)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>(0.8, 0.8, 0.8, 0.8)</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>(1.0, 1.0, 1.0, 1.0)</t>
-        </is>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/four_annular_bemt_tuning_report.xlsx
+++ b/01_Thermal/B_results/four_annular_bemt_tuning_report.xlsx
@@ -493,14 +493,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>uniform_N2_soft_rmse</t>
+          <t>uniform_N2_soft_cons</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.333686588563102</v>
+        <v>0.304553144495077</v>
       </c>
       <c r="C2" t="n">
-        <v>345.1814803740236</v>
+        <v>350.4180052329008</v>
       </c>
       <c r="D2" t="n">
         <v>1365</v>
@@ -522,17 +522,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(0.05, 0.05, 0.05, 0.05)</t>
+          <t>(0.03, 0.03, 0.03, 0.03)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(0.2, 0.2, 0.2, 0.2)</t>
+          <t>(0.1, 0.1, 0.1, 0.1)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(0.7, 0.7, 0.7, 0.7)</t>
+          <t>(0.8, 0.8, 0.8, 0.8)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -541,20 +541,20 @@
         </is>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>uniform_N2_soft_cons</t>
+          <t>uniform_N2_soft_rmse</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3337472390844793</v>
+        <v>0.3045828285540101</v>
       </c>
       <c r="C3" t="n">
-        <v>344.9414646680535</v>
+        <v>350.6949472074055</v>
       </c>
       <c r="D3" t="n">
         <v>1365</v>
@@ -576,17 +576,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(0.03, 0.03, 0.03, 0.03)</t>
+          <t>(0.05, 0.05, 0.05, 0.05)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>(0.1, 0.1, 0.1, 0.1)</t>
+          <t>(0.2, 0.2, 0.2, 0.2)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>(0.8, 0.8, 0.8, 0.8)</t>
+          <t>(0.7, 0.7, 0.7, 0.7)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="L3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3358818723527792</v>
+        <v>0.3051273561044199</v>
       </c>
       <c r="C4" t="n">
-        <v>338.4345802010039</v>
+        <v>349.371129912444</v>
       </c>
       <c r="D4" t="n">
         <v>1365</v>
@@ -655,14 +655,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mixed_soft_l1_alt_bias</t>
+          <t>mixed_soft_l1_cons_split</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3358885923134106</v>
+        <v>0.305131961716154</v>
       </c>
       <c r="C5" t="n">
-        <v>343.8421576726826</v>
+        <v>349.2691962599561</v>
       </c>
       <c r="D5" t="n">
         <v>1365</v>
@@ -679,22 +679,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(1.5, 1.0, 1.5, 1.0)</t>
+          <t>(1.0, 1.5, 1.0, 1.5)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(0.03, 0.05, 0.03, 0.05)</t>
+          <t>(0.03, 0.03, 0.03, 0.03)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>(0.1, 0.2, 0.1, 0.2)</t>
+          <t>(0.1, 0.1, 0.1, 0.1)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>(0.8, 0.7, 0.8, 0.7)</t>
+          <t>(0.8, 0.8, 0.8, 0.8)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mixed_soft_l1_cons_split</t>
+          <t>mixed_soft_l1_alt_bias</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3359584202335988</v>
+        <v>0.3098818940246092</v>
       </c>
       <c r="C6" t="n">
-        <v>338.2291793165646</v>
+        <v>342.2244928120672</v>
       </c>
       <c r="D6" t="n">
         <v>1365</v>
@@ -733,22 +733,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(1.0, 1.5, 1.0, 1.5)</t>
+          <t>(1.5, 1.0, 1.5, 1.0)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(0.03, 0.03, 0.03, 0.03)</t>
+          <t>(0.03, 0.05, 0.03, 0.05)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>(0.1, 0.1, 0.1, 0.1)</t>
+          <t>(0.1, 0.2, 0.1, 0.2)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>(0.8, 0.8, 0.8, 0.8)</t>
+          <t>(0.8, 0.7, 0.8, 0.7)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3367884401889317</v>
+        <v>0.3100196428754869</v>
       </c>
       <c r="C7" t="n">
-        <v>342.8112303352777</v>
+        <v>340.8822386356892</v>
       </c>
       <c r="D7" t="n">
         <v>1365</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3458484047863049</v>
+        <v>0.3169233960477184</v>
       </c>
       <c r="C8" t="n">
-        <v>333.9196258595847</v>
+        <v>338.3420860888297</v>
       </c>
       <c r="D8" t="n">
         <v>1365</v>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3573173951806795</v>
+        <v>0.3284161878752256</v>
       </c>
       <c r="C9" t="n">
-        <v>378.9455554984523</v>
+        <v>377.6340455972056</v>
       </c>
       <c r="D9" t="n">
         <v>1365</v>
